--- a/data/transformed/estadoObra_filtrado.xlsx
+++ b/data/transformed/estadoObra_filtrado.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>sucursal</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Proyecto</t>
+          <t>proyecto</t>
         </is>
       </c>
     </row>

--- a/data/transformed/estadoObra_filtrado.xlsx
+++ b/data/transformed/estadoObra_filtrado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,18 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
